--- a/DOSSIES_MULTIFORMATO/SEDUC/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEDUC/dossie.xlsx
@@ -696,12 +696,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020NE02645</t>
+          <t>2020NE02643</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3771406.8</v>
+        <v>407376.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -719,19 +719,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ATENDER AO CONTRATO Nº 14/2018, REFERENTE PRESTAÇÃO DE SERVIÇOS TÉCNICOS PARA MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM.</t>
+          <t>ATENDER AO CONTRATO Nº 02/2015, REFERENTE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020NE02643</t>
+          <t>2020NE02645</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>407376.7</v>
+        <v>3771406.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ATENDER AO CONTRATO Nº 02/2015, REFERENTE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL.</t>
+          <t>ATENDER AO CONTRATO Nº 14/2018, REFERENTE PRESTAÇÃO DE SERVIÇOS TÉCNICOS PARA MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM.</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2017NE00580</t>
+          <t>2017NE00578</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SERV. PROCESSAMENTO DE DADOS</t>
+          <t>PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2017NE00578</t>
+          <t>2017NE00580</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -925,19 +925,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PROCESSAMENTO DE DADOS</t>
+          <t>SERV. PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2019NE07576</t>
+          <t>2019NE07578</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>244426.02</v>
+        <v>9428517</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -955,19 +955,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ATENDER AO CT. 02/2015</t>
+          <t>ATENDER AO CT. 14/2018</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2019NE07578</t>
+          <t>2019NE07576</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9428517</v>
+        <v>244426.02</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ATENDER AO CT. 14/2018</t>
+          <t>ATENDER AO CT. 02/2015</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024NE0009311</t>
+          <t>2024NE0009310</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20/2022</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3358031.83</v>
+        <v>5835123.56</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024NE0009310</t>
+          <t>2024NE0009311</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>20/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5835123.56</v>
+        <v>3358031.83</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 04.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025NE0011395</t>
+          <t>2025NE0011398</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>251.86</v>
+        <v>12.28</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO 2025NE0000648,EM ATENDIMENTO AO DECRETO DE ENCERRAMENTO Nº 52770 DE 21 DE OUTUBRO DE 2025.</t>
+          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO 2025NE000497702812,EM ATENDIMENTO AO DECRETO DE ENCERRAMENTO Nº 52770 DE 21 DE OUTUBRO DE 2025.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025NE0011398</t>
+          <t>2025NE0011395</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.28</v>
+        <v>251.86</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO 2025NE000497702812,EM ATENDIMENTO AO DECRETO DE ENCERRAMENTO Nº 52770 DE 21 DE OUTUBRO DE 2025.</t>
+          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO 2025NE0000648,EM ATENDIMENTO AO DECRETO DE ENCERRAMENTO Nº 52770 DE 21 DE OUTUBRO DE 2025.</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2023NE0008924</t>
+          <t>2023NE0008923</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>83395.57000000001</v>
+        <v>296020.56</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1419,19 +1419,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 002/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2023NE0008923</t>
+          <t>2023NE0008924</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>296020.56</v>
+        <v>83395.57000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 002/2021 AD: 02.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -1512,14 +1512,10 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2017NE06887</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>161/2016</t>
-        </is>
-      </c>
+          <t>2017NE06884</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>29/09/2017</t>
@@ -1535,17 +1531,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Para atender no aditivo do contrato nº 161/2016 que tem como objeto: serviços de desenvolvimento e implantação de software (SIGEAM) em atendimento as Escolas Estaduais da Rede Publica de Ensino.</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2017NE06884</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>2017NE06887</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>161/2016</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>29/09/2017</t>
@@ -1561,14 +1561,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>Para atender no aditivo do contrato nº 161/2016 que tem como objeto: serviços de desenvolvimento e implantação de software (SIGEAM) em atendimento as Escolas Estaduais da Rede Publica de Ensino.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2016NE05112</t>
+          <t>2016NE05111</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>485253.11</v>
+        <v>1000000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2016NE05111</t>
+          <t>2016NE05112</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1000000</v>
+        <v>485253.11</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1744,12 +1744,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2021NE0000372</t>
+          <t>2021NE0000408</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>54/2017</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>888061.6800000001</v>
+        <v>6003.06</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA - FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC.</t>
+          <t>ATENDER DESPESAS DO 1º TRIMESTRE DE 2021 DO CT 054/2017 - CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM PARA USO E MANUTENÇÃO DO SISTEMA DE GESTÃO DE PROJETOS - SIGPRO.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2021NE0000408</t>
+          <t>2021NE0000372</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>54/2017</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6003.06</v>
+        <v>888061.6800000001</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ATENDER DESPESAS DO 1º TRIMESTRE DE 2021 DO CT 054/2017 - CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM PARA USO E MANUTENÇÃO DO SISTEMA DE GESTÃO DE PROJETOS - SIGPRO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA - FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC.</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2022NE0008504</t>
+          <t>2022NE0008505</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>935.58</v>
+        <v>170000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1883,14 +1883,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>REFORÇO À NOTA DE EMPENHO Nº 2022NE0004479, PARA ATENDER DESPESAS DO CONTRATO Nº CT-00054/2017-SEDUC, REFERENTE A SERVIÇOS PARA CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM PARA USO E MANUTENÇÃO DO SIGPRO.</t>
+          <t>ATENDER DESPESAS CONTRATUAIS DO CT 054/2017-SEDUC, REFERENTE A CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM PARA USO E MANUTENÇÃO DO SISTEMA DE GESTÃO DE PROJETOS - SIGPRO.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2022NE0008505</t>
+          <t>2022NE0008504</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>170000</v>
+        <v>935.58</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ATENDER DESPESAS CONTRATUAIS DO CT 054/2017-SEDUC, REFERENTE A CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM PARA USO E MANUTENÇÃO DO SISTEMA DE GESTÃO DE PROJETOS - SIGPRO.</t>
+          <t>REFORÇO À NOTA DE EMPENHO Nº 2022NE0004479, PARA ATENDER DESPESAS DO CONTRATO Nº CT-00054/2017-SEDUC, REFERENTE A SERVIÇOS PARA CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM PARA USO E MANUTENÇÃO DO SIGPRO.</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2021NE0004733</t>
+          <t>2021NE0004730</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5835123.56</v>
+        <v>3771406.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2003,19 +2003,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SERVICOS TÉCNICOS PROFISSIONAIS DE TIC;SERVIÇOS DE CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MÓDULO DE GESTÃO DE ATENDIMENTO A CENTRAL DA SEDUC;COMPLEMENTO DE QB;2021NE150</t>
+          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO DE MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM;COMPLEMENTO DE QB;2021NE1456;CT 14/2018;3° TERMO ADITIVO ;R$ 22.628.440,80</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2021NE0004730</t>
+          <t>2021NE0004733</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3771406.8</v>
+        <v>5835123.56</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO DE MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM;COMPLEMENTO DE QB;2021NE1456;CT 14/2018;3° TERMO ADITIVO ;R$ 22.628.440,80</t>
+          <t>SERVICOS TÉCNICOS PROFISSIONAIS DE TIC;SERVIÇOS DE CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MÓDULO DE GESTÃO DE ATENDIMENTO A CENTRAL DA SEDUC;COMPLEMENTO DE QB;2021NE150</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024NE0011455</t>
+          <t>2024NE0011462</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2149,14 +2149,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE0003799, EM ATENDIMENTO AO DECRETO Nº 50.522, PUBLICADO NO DIÁRIO OFICIAL DO ESTADO DO AMAZONAS NO DIA 22 DE OUTUBRO DE 2024, QUE DISPÕE SOBRE NORMAS E PROCED</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE0008475, EM ATENDIMENTO AO DECRETO Nº 50.522, PUBLICADO NO DIÁRIO OFICIAL DO ESTADO DO AMAZONAS NO DIA 22 DE OUTUBRO DE 2024, QUE DISPÕE SOBRE NORMAS E PROCED</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024NE0011468</t>
+          <t>2024NE0011459</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.32</v>
+        <v>0.02</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE0009310, EM ATENDIMENTO AO DECRETO Nº 50.522, PUBLICADO NO DIÁRIO OFICIAL DO ESTADO DO AMAZONAS NO DIA 22 DE OUTUBRO DE 2024, QUE DISPÕE SOBRE NORMAS E PROCED</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE0003959, EM ATENDIMENTO AO DECRETO Nº 50.522, PUBLICADO NO DIÁRIO OFICIAL DO ESTADO DO AMAZONAS NO DIA 22 DE OUTUBRO DE 2024, QUE DISPÕE SOBRE NORMAS E PROCED</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024NE0011459</t>
+          <t>2024NE0011468</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.02</v>
+        <v>1.32</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2227,14 +2227,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE0003959, EM ATENDIMENTO AO DECRETO Nº 50.522, PUBLICADO NO DIÁRIO OFICIAL DO ESTADO DO AMAZONAS NO DIA 22 DE OUTUBRO DE 2024, QUE DISPÕE SOBRE NORMAS E PROCED</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE0009310, EM ATENDIMENTO AO DECRETO Nº 50.522, PUBLICADO NO DIÁRIO OFICIAL DO ESTADO DO AMAZONAS NO DIA 22 DE OUTUBRO DE 2024, QUE DISPÕE SOBRE NORMAS E PROCED</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024NE0011462</t>
+          <t>2024NE0011455</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE0008475, EM ATENDIMENTO AO DECRETO Nº 50.522, PUBLICADO NO DIÁRIO OFICIAL DO ESTADO DO AMAZONAS NO DIA 22 DE OUTUBRO DE 2024, QUE DISPÕE SOBRE NORMAS E PROCED</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE0003799, EM ATENDIMENTO AO DECRETO Nº 50.522, PUBLICADO NO DIÁRIO OFICIAL DO ESTADO DO AMAZONAS NO DIA 22 DE OUTUBRO DE 2024, QUE DISPÕE SOBRE NORMAS E PROCED</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2019NE07442</t>
+          <t>2019NE07445</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>244426.02</v>
+        <v>733271.42</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2305,14 +2305,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 019/2019 PARA FINS DE REPROGRAMAÇÃO DO CRONOGRAMA FINANCEIRO DO EXERCÍCIO DE 2019, REFERENTE A SALDO DE EMPENHOS, ATENDENDO O DECRETO DE ENCERRAMEN</t>
+          <t>ANULAÇÃO TOTAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 05779/2019 PARA FINS DE REPROGRAMAÇÃO DO CRONOGRAMA FINANCEIRO DO EXERCÍCIO DE 2019, REFERENTE A SALDO DE EMPENHOS, ATENDENDO O DECRETO DE ENCERRAM</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2019NE07443</t>
+          <t>2019NE07444</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>227725.18</v>
+        <v>733280.58</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2331,14 +2331,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 01963/2019 PARA FINS DE REPROGRAMAÇÃO DO CRONOGRAMA FINANCEIRO DO EXERCÍCIO DE 2019, REFERENTE A SALDO DE EMPENHOS, ATENDENDO O DECRETO DE ENCERR</t>
+          <t>ANULAÇÃO TOTAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 03862/2019 PARA FINS DE REPROGRAMAÇÃO DO CRONOGRAMA FINANCEIRO DO EXERCÍCIO DE 2019, REFERENTE A SALDO DE EMPENHOS, ATENDENDO O DECRETO DE ENCERRAM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2019NE07444</t>
+          <t>2019NE07443</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>733280.58</v>
+        <v>227725.18</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2357,14 +2357,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 03862/2019 PARA FINS DE REPROGRAMAÇÃO DO CRONOGRAMA FINANCEIRO DO EXERCÍCIO DE 2019, REFERENTE A SALDO DE EMPENHOS, ATENDENDO O DECRETO DE ENCERRAM</t>
+          <t>ANULAÇÃO PARCIAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 01963/2019 PARA FINS DE REPROGRAMAÇÃO DO CRONOGRAMA FINANCEIRO DO EXERCÍCIO DE 2019, REFERENTE A SALDO DE EMPENHOS, ATENDENDO O DECRETO DE ENCERR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2019NE07445</t>
+          <t>2019NE07442</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>733271.42</v>
+        <v>244426.02</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2383,28 +2383,24 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 05779/2019 PARA FINS DE REPROGRAMAÇÃO DO CRONOGRAMA FINANCEIRO DO EXERCÍCIO DE 2019, REFERENTE A SALDO DE EMPENHOS, ATENDENDO O DECRETO DE ENCERRAM</t>
+          <t>ANULAÇÃO TOTAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 019/2019 PARA FINS DE REPROGRAMAÇÃO DO CRONOGRAMA FINANCEIRO DO EXERCÍCIO DE 2019, REFERENTE A SALDO DE EMPENHOS, ATENDENDO O DECRETO DE ENCERRAMEN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2016NE09727</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P.180/2016</t>
-        </is>
-      </c>
+          <t>2016NE09744</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>27/12/2016</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1283878.25</v>
+        <v>67572.53999999999</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2413,24 +2409,28 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>indenização</t>
+          <t>INDENIZAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2016NE09744</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>2016NE09727</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P.180/2016</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>27/12/2016</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>67572.53999999999</v>
+        <v>1283878.25</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2439,14 +2439,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>INDENIZAÇÃO</t>
+          <t>indenização</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2023NE0008864</t>
+          <t>2023NE0008866</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>83395.57000000001</v>
+        <v>296020.56</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO ORÇAMENTÁRIO DA NOTA DE EMPENHO 2023NE0006095, PARA AJUSTE DE FONTE</t>
+          <t>ANULAÇÃO DO SALDO ORÇAMENTÁRIO DA NOTA DE EMPENHO 2023NE0006096, PARA AJUSTE DE FONTE</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2023NE0008866</t>
+          <t>2023NE0008864</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>296020.56</v>
+        <v>83395.57000000001</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO ORÇAMENTÁRIO DA NOTA DE EMPENHO 2023NE0006096, PARA AJUSTE DE FONTE</t>
+          <t>ANULAÇÃO DO SALDO ORÇAMENTÁRIO DA NOTA DE EMPENHO 2023NE0006095, PARA AJUSTE DE FONTE</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2021NE0003529</t>
+          <t>2021NE0003528</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>369600</v>
+        <v>2731200.25</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2021NE0003528</t>
+          <t>2021NE0003529</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2731200.25</v>
+        <v>369600</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2674,12 +2674,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025NE0006225</t>
+          <t>2025NE0006209</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>20/2022</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1635948.77</v>
+        <v>1450847.54</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2697,19 +2697,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DE GESTÃO DE ATENDIMENTO DA SEDUC/AM. TC: 0023/2021 AD: 05.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025NE0006209</t>
+          <t>2025NE0006225</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20/2022</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1450847.54</v>
+        <v>1635948.77</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2727,21 +2727,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DE GESTÃO DE ATENDIMENTO DA SEDUC/AM. TC: 0023/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2018NE04045</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>91/2016</t>
-        </is>
-      </c>
+          <t>2018NE04044</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>26/06/2018</t>
@@ -2757,17 +2753,21 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PARA ATENDER EM DESPESAS COM O CONTRATO N. 91/2016. OBJETO: SERVIÇOS DE CONSULTORIA, TREINAMENTO E MANUTENÇÃO DO SIGEAM, QUE ATENDE AS ESCOLAS DA REDE ESTADUAL DE ENSINO.</t>
+          <t>ANULAÇÃO TOTAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 3554/2018 POR TER SIDO IMPRESSA SEM HISTÓRICO</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2018NE04044</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>2018NE04045</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>91/2016</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>26/06/2018</t>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DOS RECURSOS DA NOTA DE EMPENHO DE N. 3554/2018 POR TER SIDO IMPRESSA SEM HISTÓRICO</t>
+          <t>PARA ATENDER EM DESPESAS COM O CONTRATO N. 91/2016. OBJETO: SERVIÇOS DE CONSULTORIA, TREINAMENTO E MANUTENÇÃO DO SIGEAM, QUE ATENDE AS ESCOLAS DA REDE ESTADUAL DE ENSINO.</t>
         </is>
       </c>
     </row>
@@ -2849,11 +2849,7 @@
           <t>2016NE08596</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>161/2016</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>25/10/2016</t>
@@ -2879,7 +2875,11 @@
           <t>2016NE08596</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>161/2016</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>25/10/2016</t>
@@ -2932,7 +2932,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025NE0002282</t>
+          <t>2025NE0002276</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1333679.43</v>
+        <v>725439.59</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2955,14 +2955,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trata-se os autos de solicitação de pagamento sem cobertura contratual referente aos prestação de serviços técnicos especializados para a manutenção operacional, corretiva e evolutiva do SIGEAM - Sist</t>
+          <t xml:space="preserve">Tratam os autos de solicitação de pagamento de reconhecimento de dívidas, referentes aos serviços de técnicosespecializados para a manutenção operacional, corretiva e evolutiva do SIGEAM - Sistema de </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025NE0002281</t>
+          <t>2025NE0002283</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1090274.23</v>
+        <v>1333679.43</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2985,14 +2985,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tratam os autos de solicitação de pagamento de reconhecimento de dívida, referentes aos serviços prestados sem cobertura contratual,sendo eles, técnicos especializados para a manutenção operacional, c</t>
+          <t>Trata-se os autos de solicitação de pagamento sem cobertura contratual referente aos prestação de serviços técnicos especializados para a manutenção operacional, corretiva e evolutiva do SIGEAM - Sist</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025NE0002280</t>
+          <t>2025NE0002279</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>989631.47</v>
+        <v>734682.26</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trata-se os autos de solicitação de pagamento sem cobertura contratual referente aos prestação de serviços técnicos especializados para a manutenção operacional, corretiva e evolutiva do SIGEAM</t>
+          <t>Tratam os autos de solicitação de pagamento de reconhecimento de dívida, referentes aos serviços prestados sem cobertura contratual,sendo eles, técnicos especializados para a manutenção operacional, c</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025NE0002279</t>
+          <t>2025NE0002280</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>734682.26</v>
+        <v>989631.47</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3075,14 +3075,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tratam os autos de solicitação de pagamento de reconhecimento de dívida, referentes aos serviços prestados sem cobertura contratual,sendo eles, técnicos especializados para a manutenção operacional, c</t>
+          <t>Trata-se os autos de solicitação de pagamento sem cobertura contratual referente aos prestação de serviços técnicos especializados para a manutenção operacional, corretiva e evolutiva do SIGEAM</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025NE0002283</t>
+          <t>2025NE0002281</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1333679.43</v>
+        <v>1090274.23</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3105,14 +3105,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trata-se os autos de solicitação de pagamento sem cobertura contratual referente aos prestação de serviços técnicos especializados para a manutenção operacional, corretiva e evolutiva do SIGEAM - Sist</t>
+          <t>Tratam os autos de solicitação de pagamento de reconhecimento de dívida, referentes aos serviços prestados sem cobertura contratual,sendo eles, técnicos especializados para a manutenção operacional, c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025NE0002276</t>
+          <t>2025NE0002282</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>725439.59</v>
+        <v>1333679.43</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tratam os autos de solicitação de pagamento de reconhecimento de dívidas, referentes aos serviços de técnicosespecializados para a manutenção operacional, corretiva e evolutiva do SIGEAM - Sistema de </t>
+          <t>Trata-se os autos de solicitação de pagamento sem cobertura contratual referente aos prestação de serviços técnicos especializados para a manutenção operacional, corretiva e evolutiva do SIGEAM - Sist</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024NE0004403</t>
+          <t>2024NE0004405</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>95691.2</v>
+        <v>1155815.42</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3539,14 +3539,14 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE000011, CONSIDERANDO O TÉRMINO DA VIGÊNCIA DO 2º TERMO ADITIVO AO CONTRATO Nº 02/2021. EM ATENDIMENTO AO DESPACHO EXARADO PELA GERÊNCIA DE SISTEMAS DE INFORMA</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE002014, CONSIDERANDO O TÉRMINO DA VIGÊNCIA DO 2º TERMO ADITIVO AO CONTRATO Nº 02/2021. EM ATENDIMENTO AO DESPACHO EXARADO PELA GERÊNCIA DE SISTEMAS DE INFORMA</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2024NE0004405</t>
+          <t>2024NE0004403</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1155815.42</v>
+        <v>95691.2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE002014, CONSIDERANDO O TÉRMINO DA VIGÊNCIA DO 2º TERMO ADITIVO AO CONTRATO Nº 02/2021. EM ATENDIMENTO AO DESPACHO EXARADO PELA GERÊNCIA DE SISTEMAS DE INFORMA</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO 2024NE000011, CONSIDERANDO O TÉRMINO DA VIGÊNCIA DO 2º TERMO ADITIVO AO CONTRATO Nº 02/2021. EM ATENDIMENTO AO DESPACHO EXARADO PELA GERÊNCIA DE SISTEMAS DE INFORMA</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2022NE0001493</t>
+          <t>2022NE0001503</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>20/2022</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5531396.64</v>
+        <v>6606733.25</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3625,19 +3625,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO TÉCNICO ESPECIALIZADO PARA MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM. SALDO REMANESCENTE;COMPLEMENTO DE QB;2022NE0241;CT 14/2018;3° TERMO</t>
+          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICO</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2022NE0001503</t>
+          <t>2022NE0001493</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>20/2022</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6606733.25</v>
+        <v>5531396.64</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3655,14 +3655,14 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICO</t>
+          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO TÉCNICO ESPECIALIZADO PARA MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM. SALDO REMANESCENTE;COMPLEMENTO DE QB;2022NE0241;CT 14/2018;3° TERMO</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2017NE01521</t>
+          <t>2017NE01520</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6720.47</v>
+        <v>60483.79</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2017NE01520</t>
+          <t>2017NE01521</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>60483.79</v>
+        <v>6720.47</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2022NE0008950</t>
+          <t>2022NE0008947</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>135565.31</v>
+        <v>5375559.49</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2022NE0008949</t>
+          <t>2022NE0008948</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>94933.91</v>
+        <v>1681751.82</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2022NE0008948</t>
+          <t>2022NE0008949</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1681751.82</v>
+        <v>94933.91</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2022NE0008947</t>
+          <t>2022NE0008950</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5375559.49</v>
+        <v>135565.31</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3912,14 +3912,10 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2020NE01548</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>14/2018</t>
-        </is>
-      </c>
+          <t>2020NE01550</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
           <t>20/05/2020</t>
@@ -3935,7 +3931,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RENOVAÇÃO AO CONTRATO 14/2018</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO</t>
         </is>
       </c>
     </row>
@@ -3972,10 +3968,14 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020NE01550</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>2020NE01548</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>14/2018</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
           <t>20/05/2020</t>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO</t>
+          <t>RENOVAÇÃO AO CONTRATO 14/2018</t>
         </is>
       </c>
     </row>
@@ -4024,10 +4024,14 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2023NE0000008</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>2023NE0000006</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>14/2018</t>
+        </is>
+      </c>
       <c r="C120" t="inlineStr">
         <is>
           <t>20/01/2023</t>
@@ -4043,21 +4047,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 2023NE00000006, PARA CORREÇÃO DA DATA DE EMISSÃO</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM REF AO 4º TERMO ADITIVO AO CONTRATO Nº 14/2018, FIRMADO COM ESTA SECRETARIA PELO PERÍODO </t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2023NE0000006</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>14/2018</t>
-        </is>
-      </c>
+          <t>2023NE0000008</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
           <t>20/01/2023</t>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM REF AO 4º TERMO ADITIVO AO CONTRATO Nº 14/2018, FIRMADO COM ESTA SECRETARIA PELO PERÍODO </t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 2023NE00000006, PARA CORREÇÃO DA DATA DE EMISSÃO</t>
         </is>
       </c>
     </row>
@@ -4110,14 +4110,10 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2016NE06984</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>128/2016</t>
-        </is>
-      </c>
+          <t>2016NE06983</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>19/08/2016</t>
@@ -4133,7 +4129,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LOCAÇÃO DE SOFTWARE</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
@@ -4170,10 +4166,14 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2016NE06983</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>2016NE06984</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>128/2016</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
           <t>19/08/2016</t>
@@ -4189,19 +4189,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>LOCAÇÃO DE SOFTWARE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025NE0001095</t>
+          <t>2025NE0001094</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2774901.44</v>
+        <v>900690.91</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4219,19 +4219,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE DO CONTRATO Nº 23/2021. OBJETO: SERVIÇOS DE CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MÓDULO DE GESTÃO DE ATENDIMENTO, DESTINADO À CENTRAL DE ATENDIMENT</t>
+          <t>SALDO REMANESCENTE DO CONTRATO Nº 02/2021. OBJETO: SERVIÇOS DE INFORMÁTICA PARA EXECUÇÃO DO SISTEMA PRODAM RH - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025NE0001094</t>
+          <t>2025NE0001095</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>900690.91</v>
+        <v>2774901.44</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE DO CONTRATO Nº 02/2021. OBJETO: SERVIÇOS DE INFORMÁTICA PARA EXECUÇÃO DO SISTEMA PRODAM RH - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL.</t>
+          <t>SALDO REMANESCENTE DO CONTRATO Nº 23/2021. OBJETO: SERVIÇOS DE CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MÓDULO DE GESTÃO DE ATENDIMENTO, DESTINADO À CENTRAL DE ATENDIMENT</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4376,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025NE0007845</t>
+          <t>2025NE0007857</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>624814.08</v>
+        <v>2917741.06</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4399,19 +4399,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 04.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DE GESTÃO DE ATENDIMENTO DA SEDUC/AM. TC: 0023/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025NE0007857</t>
+          <t>2025NE0007845</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2917741.06</v>
+        <v>624814.08</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4429,28 +4429,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DE GESTÃO DE ATENDIMENTO DA SEDUC/AM. TC: 0023/2021 AD: 05.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2016NE05695</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>91/2016</t>
-        </is>
-      </c>
+          <t>2016NE05694</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
           <t>18/07/2016</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1068769.15</v>
+        <v>1194922.67</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4459,24 +4455,28 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>TECNOLOGIA DA INFORMAÇÃO</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO DE N. 5396/2016 POR TER SIDO EMPENHADO A MAIOR</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2016NE05694</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>2016NE05695</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>91/2016</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>18/07/2016</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1194922.67</v>
+        <v>1068769.15</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4485,19 +4485,19 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO DE N. 5396/2016 POR TER SIDO EMPENHADO A MAIOR</t>
+          <t>TECNOLOGIA DA INFORMAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2024NE0003352</t>
+          <t>2024NE0003351</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1458870.53</v>
+        <v>1885703.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4515,19 +4515,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE DO 3º TERMO ADITIVO AO CONTRATO Nº 23/2021. OBJETO: SERVIÇOS DE CONTACT CENTER, COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MÓDULO DE GESTÃO DE ATENDIMENTO, UTILIZANDO M</t>
+          <t>SALDO REMANESCENTE DO 5º TERMO ADITIVO AO CONTRATO Nº 14/2018. OBJETO: SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL D</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2024NE0003351</t>
+          <t>2024NE0003352</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1885703.4</v>
+        <v>1458870.53</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4545,19 +4545,19 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE DO 5º TERMO ADITIVO AO CONTRATO Nº 14/2018. OBJETO: SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL D</t>
+          <t>SALDO REMANESCENTE DO 3º TERMO ADITIVO AO CONTRATO Nº 23/2021. OBJETO: SERVIÇOS DE CONTACT CENTER, COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MÓDULO DE GESTÃO DE ATENDIMENTO, UTILIZANDO M</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2020NE00350</t>
+          <t>2020NE00365</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>54/2017</t>
+          <t>91/2016</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4000</v>
+        <v>890640.96</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ATENDER SALDO DO CT.00054/2017 - REF CUSTOMIZAÇÃO IMPLANTAÇÃO E HOSPEDAGEM DO SIGPRO.</t>
+          <t>ATENDER CT.00091/2016-SEDUC - DESENVOLVIMENTO E IMPLANTAÇÃO DO SIGEAM</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2020NE00364</t>
+          <t>2020NE00349</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>222660.24</v>
+        <v>206245.7</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4601,14 +4601,14 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO Nº 2020NE00126, CORRESPONDENTE AO CT.00091/2016-SEDUC, PARA PERMUTA DE FONTE.</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO Nº 2020NE00130, CORRESPONDENTE AO CT.00054/2017-SEDUC, PARA PERMUTA DE FONTE.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2020NE00349</t>
+          <t>2020NE00364</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>206245.7</v>
+        <v>222660.24</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4627,19 +4627,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO Nº 2020NE00130, CORRESPONDENTE AO CT.00054/2017-SEDUC, PARA PERMUTA DE FONTE.</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO Nº 2020NE00126, CORRESPONDENTE AO CT.00091/2016-SEDUC, PARA PERMUTA DE FONTE.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2020NE00365</t>
+          <t>2020NE00350</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>91/2016</t>
+          <t>54/2017</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>890640.96</v>
+        <v>4000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ATENDER CT.00091/2016-SEDUC - DESENVOLVIMENTO E IMPLANTAÇÃO DO SIGEAM</t>
+          <t>ATENDER SALDO DO CT.00054/2017 - REF CUSTOMIZAÇÃO IMPLANTAÇÃO E HOSPEDAGEM DO SIGPRO.</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>NE 7822 DE 17/11/2015 R$ 1.485.253,11 Contrato 235/2010 - SIGEAM ON LINE</t>
+          <t>SER. PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SER. PROCESSAMENTO DE DADOS</t>
+          <t>NE 7822 DE 17/11/2015 R$ 1.485.253,11 Contrato 235/2010 - SIGEAM ON LINE</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2017NE01364</t>
+          <t>2017NE01365</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>54/2017</t>
+          <t>91/2016</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>68548.3</v>
+        <v>7616.48</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4837,24 +4837,28 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Serviços customização.</t>
+          <t>serviços customização.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2017NE01518</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>2017NE01280</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>91/2016</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr">
         <is>
           <t>17/03/2017</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>68548.3</v>
+        <v>712512.77</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4863,7 +4867,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Anulação</t>
+          <t>Consultoria</t>
         </is>
       </c>
     </row>
@@ -4896,21 +4900,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2017NE01280</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>91/2016</t>
-        </is>
-      </c>
+          <t>2017NE01518</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
           <t>17/03/2017</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>712512.77</v>
+        <v>68548.3</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4919,19 +4919,19 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Anulação</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2017NE01365</t>
+          <t>2017NE01364</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>91/2016</t>
+          <t>54/2017</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>7616.48</v>
+        <v>68548.3</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>serviços customização.</t>
+          <t>Serviços customização.</t>
         </is>
       </c>
     </row>
@@ -5016,10 +5016,14 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2018NE01512</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
+          <t>2018NE01513</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2/2015</t>
+        </is>
+      </c>
       <c r="C154" t="inlineStr">
         <is>
           <t>16/03/2018</t>
@@ -5035,21 +5039,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>ADITIVO CT- 02/2015</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2018NE01513</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2/2015</t>
-        </is>
-      </c>
+          <t>2018NE01512</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
           <t>16/03/2018</t>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ADITIVO CT- 02/2015</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
@@ -5192,12 +5192,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2018NE03554</t>
+          <t>2018NE03573</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>91/2016</t>
+          <t>161/2016</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2493794.69</v>
+        <v>1010600.98</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5215,19 +5215,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>PARA ATENDER EM DESPESAS COM O CONTRATO N. 91/2016. OBJETO: SERVIÇOS DE CONSULTORIA, TREINAMENTO E MANUTENÇÃO DO SIGEAM, QUE ATENDE AS ESCOLAS DA REDE ESTADUAL DE ENSINO.</t>
+          <t>PARA ATENDER A PAGAMENTO/EXERCÍCIOS ANTERIORES, PERÍODO NOVEMBRO DE 2017, DE SERVIÇOS DE DESENVOLVIMENTO E IMPLANTAÇÃO DE SOFTWARE (SIGEAM) QUE ATENDEU AS NECESSIDADES DESTA SECRETARIA JUNTO AS ESCOLA</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2018NE03573</t>
+          <t>2018NE03554</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>161/2016</t>
+          <t>91/2016</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1010600.98</v>
+        <v>2493794.69</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5245,14 +5245,14 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>PARA ATENDER A PAGAMENTO/EXERCÍCIOS ANTERIORES, PERÍODO NOVEMBRO DE 2017, DE SERVIÇOS DE DESENVOLVIMENTO E IMPLANTAÇÃO DE SOFTWARE (SIGEAM) QUE ATENDEU AS NECESSIDADES DESTA SECRETARIA JUNTO AS ESCOLA</t>
+          <t>PARA ATENDER EM DESPESAS COM O CONTRATO N. 91/2016. OBJETO: SERVIÇOS DE CONSULTORIA, TREINAMENTO E MANUTENÇÃO DO SIGEAM, QUE ATENDE AS ESCOLAS DA REDE ESTADUAL DE ENSINO.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2023NE0004028</t>
+          <t>2023NE04028</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2019297.86</v>
+        <v>2019287.86</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5275,14 +5275,14 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
+          <t>5º Termo Aditivo, prorrogação de prazo.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2023NE04028</t>
+          <t>2023NE0004028</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2019287.86</v>
+        <v>2019297.86</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>5º Termo Aditivo, prorrogação de prazo.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -5342,12 +5342,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2024NE0008473</t>
+          <t>2024NE0008475</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>20/2022</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>296019.94</v>
+        <v>1934977</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5365,19 +5365,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 03.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2024NE0008475</t>
+          <t>2024NE0008473</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>20/2022</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1934977</v>
+        <v>296019.94</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5462,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025NE0003892</t>
+          <t>2025NE0003893</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>624814.08</v>
+        <v>1410154.86</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5485,19 +5485,19 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 04.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DE GESTÃO DE ATENDIMENTO DA SEDUC/AM. TC: 0023/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025NE0003893</t>
+          <t>2025NE0003892</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5506,7 +5506,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1410154.86</v>
+        <v>624814.08</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5515,19 +5515,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DE GESTÃO DE ATENDIMENTO DA SEDUC/AM. TC: 0023/2021 AD: 04.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2024NE0003958</t>
+          <t>2024NE0003956</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1458870.53</v>
+        <v>296019.94</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5545,19 +5545,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 03.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2024NE0003955</t>
+          <t>2024NE0003959</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>20/2022</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1752108.94</v>
+        <v>1475162.08</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5575,19 +5575,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2024NE0003959</t>
+          <t>2024NE0003955</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>20/2022</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1475162.08</v>
+        <v>1752108.94</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2024NE0003956</t>
+          <t>2024NE0003958</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>296019.94</v>
+        <v>1458870.53</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 03.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2024NE0002483</t>
+          <t>2024NE0002485</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>3771406.8</v>
+        <v>2917741.06</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5725,14 +5725,14 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2024NE0002485</t>
+          <t>2024NE0002483</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2917741.06</v>
+        <v>3771406.8</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 03.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -5792,12 +5792,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2022NE0004038</t>
+          <t>2022NE0004032</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>54/2021</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>543424.01</v>
+        <v>1885703.4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SERVICOS TÉCNICOS PROFISSIONAIS DE TIC;SERVIÇO DE IMPLANTAÇÃO DE REPOSITRÓRIO ARQUIVÍSTICO CONFIÁVEL, MANTIDA NA ESTRUTURA DE DATA CENTER PRÓPRIA. SALDO REMANESCENTE;COMPLEMENTO DE QB;2022NE2608;CT 54</t>
+          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO TÉCNICO ESPECIALIZADO PARA MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM. SALDO REMANESCENTE;COMPLEMENTO DE QB;2022NE2921;CT 14/2018;4° TERMO</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2022NE0004032</t>
+          <t>2022NE0004038</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>54/2021</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1885703.4</v>
+        <v>543424.01</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO TÉCNICO ESPECIALIZADO PARA MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM. SALDO REMANESCENTE;COMPLEMENTO DE QB;2022NE2921;CT 14/2018;4° TERMO</t>
+          <t>SERVICOS TÉCNICOS PROFISSIONAIS DE TIC;SERVIÇO DE IMPLANTAÇÃO DE REPOSITRÓRIO ARQUIVÍSTICO CONFIÁVEL, MANTIDA NA ESTRUTURA DE DATA CENTER PRÓPRIA. SALDO REMANESCENTE;COMPLEMENTO DE QB;2022NE2608;CT 54</t>
         </is>
       </c>
     </row>
@@ -5912,12 +5912,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2020NE00126</t>
+          <t>2020NE00130</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>91/2016</t>
+          <t>54/2017</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>222660.24</v>
+        <v>206245.7</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5935,19 +5935,19 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>ATENDER CT.091/2016-SEDUC, DESENVOLVIMENTO E IMPLANTAÇÃO DO SIGEAM.</t>
+          <t>ATENDER CT.054/2017-SEDUC, FIRMADO COM A PRODAM, REF. CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM DO SIGPRO.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2020NE00130</t>
+          <t>2020NE00126</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>54/2017</t>
+          <t>91/2016</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>206245.7</v>
+        <v>222660.24</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ATENDER CT.054/2017-SEDUC, FIRMADO COM A PRODAM, REF. CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM DO SIGPRO.</t>
+          <t>ATENDER CT.091/2016-SEDUC, DESENVOLVIMENTO E IMPLANTAÇÃO DO SIGEAM.</t>
         </is>
       </c>
     </row>
@@ -6032,12 +6032,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2022NE0007459</t>
+          <t>2022NE0007460</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>20/2022</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1885703.4</v>
+        <v>1458780.89</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6055,19 +6055,19 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO TÉCNICO ESPECIALIZADO PARA MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM. SALDO REMANESCENTE;COMPLEMENTO DE QB;2022NE6242;CT 14/2018;4° TERMO</t>
+          <t>SERVICOS TÉCNICOS PROFISSIONAIS DE TIC;SERVIÇO DE OPERAÇÃO E GESTÃO DE CENTRAL DE ATENDIMENTO MULTICANAIS;COMPLEMENTO DE QB;2022NE6115;CT 23/2021;1° TERMO;R$ 17.505.370,65</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2022NE0007460</t>
+          <t>2022NE0007459</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>20/2022</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1458780.89</v>
+        <v>1885703.4</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SERVICOS TÉCNICOS PROFISSIONAIS DE TIC;SERVIÇO DE OPERAÇÃO E GESTÃO DE CENTRAL DE ATENDIMENTO MULTICANAIS;COMPLEMENTO DE QB;2022NE6115;CT 23/2021;1° TERMO;R$ 17.505.370,65</t>
+          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO TÉCNICO ESPECIALIZADO PARA MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM. SALDO REMANESCENTE;COMPLEMENTO DE QB;2022NE6242;CT 14/2018;4° TERMO</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2015NE08556</t>
+          <t>2015NE08558</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>850603.66</v>
+        <v>7635.8</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2015NE08558</t>
+          <t>2015NE08556</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7635.8</v>
+        <v>850603.66</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2023NE0004983</t>
+          <t>2023NE0004984</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -6338,7 +6338,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>619380.1800000001</v>
+        <v>1759989.84</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6347,14 +6347,14 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DE SALDO DA NOTA DE EMPENHO DE 2023NE000013</t>
+          <t>ANULAÇÃO TOTAL DE SALDO DA NOTA DE EMPENHO DE 2023NE0003892</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2023NE0004984</t>
+          <t>2023NE0004983</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1759989.84</v>
+        <v>619380.1800000001</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DE SALDO DA NOTA DE EMPENHO DE 2023NE0003892</t>
+          <t>ANULAÇÃO PARCIAL DE SALDO DA NOTA DE EMPENHO DE 2023NE000013</t>
         </is>
       </c>
     </row>
@@ -6410,12 +6410,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025NE0002812</t>
+          <t>2025NE0002818</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>20/2022</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2917561.76</v>
+        <v>434317.06</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6433,19 +6433,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DE GESTÃO DE ATENDIMENTO DA SEDUC/AM. TC: 0023/2021 AD: 04.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025NE0002818</t>
+          <t>2025NE0002812</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>20/2022</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>434317.06</v>
+        <v>2917561.76</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6463,17 +6463,21 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A SOLUÇÃO DE SISTEMA DE GESTÃO EDUCACIONAL QUE PROPORCIONE A INFORMATIZAÇÃO DOS PROCESSOS ADMINISTRATIVOS, PEDAGÓGICOS, MATRÍCULA ONLINE E DE GESTÃO DE PESSOA</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DE GESTÃO DE ATENDIMENTO DA SEDUC/AM. TC: 0023/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2018NE01832</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
+          <t>2018NE01800</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>161/2016</t>
+        </is>
+      </c>
       <c r="C203" t="inlineStr">
         <is>
           <t>10/04/2018</t>
@@ -6489,21 +6493,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>Pagamento de indenização referente ao Mês de Fevereiro/2018, NF´S: 751 A 756, dos serviços de processamento de dados contratado sem a cobertura contratual</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2018NE01800</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>161/2016</t>
-        </is>
-      </c>
+          <t>2018NE01832</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
           <t>10/04/2018</t>
@@ -6519,19 +6519,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Pagamento de indenização referente ao Mês de Fevereiro/2018, NF´S: 751 A 756, dos serviços de processamento de dados contratado sem a cobertura contratual</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025NE0000824</t>
+          <t>2025NE0000821</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1458780.88</v>
+        <v>296019.96</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6549,19 +6549,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 04.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025NE0000821</t>
+          <t>2025NE0000824</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>296019.96</v>
+        <v>1458780.88</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6579,14 +6579,14 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 03.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025NE0008389</t>
+          <t>2025NE0008390</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1333371.64</v>
+        <v>1390799.16</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025NE0008390</t>
+          <t>2025NE0008389</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1390799.16</v>
+        <v>1333371.64</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6766,14 +6766,10 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2015NE03176</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>P.222/2014</t>
-        </is>
-      </c>
+          <t>2015NE03175</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
           <t>08/05/2015</t>
@@ -6789,17 +6785,21 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>INDENIZAÇÃO</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2015NE03177</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr"/>
+          <t>2015NE03178</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>P.222/2014</t>
+        </is>
+      </c>
       <c r="C214" t="inlineStr">
         <is>
           <t>08/05/2015</t>
@@ -6815,21 +6815,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>INDENIZAÇÃO E RESTITUIÇÃO</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2015NE03178</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>P.222/2014</t>
-        </is>
-      </c>
+          <t>2015NE03177</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
           <t>08/05/2015</t>
@@ -6845,17 +6841,21 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>INDENIZAÇÃO E RESTITUIÇÃO</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2015NE03175</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr"/>
+          <t>2015NE03176</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>P.222/2014</t>
+        </is>
+      </c>
       <c r="C216" t="inlineStr">
         <is>
           <t>08/05/2015</t>
@@ -6871,14 +6871,14 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>INDENIZAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2015NE02403</t>
+          <t>2015NE02402</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>83822.44</v>
+        <v>488337.2</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6901,14 +6901,14 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>DESP DE EXERC. ANTERIORES</t>
+          <t>DESPESAS EXERCICIOS ANTERIOS</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2015NE02402</t>
+          <t>2015NE02403</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>488337.2</v>
+        <v>83822.44</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>DESPESAS EXERCICIOS ANTERIOS</t>
+          <t>DESP DE EXERC. ANTERIORES</t>
         </is>
       </c>
     </row>
@@ -7140,12 +7140,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2023NE0006095</t>
+          <t>2023NE0006096</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1885703.4</v>
+        <v>296020.56</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7163,19 +7163,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 002/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2023NE0006096</t>
+          <t>2023NE0006095</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>296020.56</v>
+        <v>1885703.4</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 002/2021 AD: 02.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM - SISTEMA DE GESTÃO EDUCACIONAL. TC: 0014/2018 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2015NE08490</t>
+          <t>2015NE08489</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>600000</v>
+        <v>2370506.22</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7283,14 +7283,14 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>TOTALIDADE DA NE 8489/2015</t>
+          <t>COMPLEMENTAÇÃO DA NE 7822/2015</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2015NE08489</t>
+          <t>2015NE08490</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>2370506.22</v>
+        <v>600000</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA NE 7822/2015</t>
+          <t>TOTALIDADE DA NE 8489/2015</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2019NE04862</t>
+          <t>2019NE04861</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1865628.52</v>
+        <v>3791481.68</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2019NE04861</t>
+          <t>2019NE04862</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3791481.68</v>
+        <v>1865628.52</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7560,12 +7560,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2016NE00400</t>
+          <t>2016NE00410</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>235/2010</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>4406250.89</v>
+        <v>185019.85</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7590,12 +7590,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2016NE00410</t>
+          <t>2016NE00400</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>235/2010</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>185019.85</v>
+        <v>4406250.89</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2019NE06792</t>
+          <t>2019NE06791</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>3680635.32</v>
+        <v>90771.48</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2019NE06791</t>
+          <t>2019NE06792</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>90771.48</v>
+        <v>3680635.32</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7680,10 +7680,14 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2015NE08488</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
+          <t>2015NE08457</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>235/2010</t>
+        </is>
+      </c>
       <c r="C244" t="inlineStr">
         <is>
           <t>03/12/2015</t>
@@ -7699,24 +7703,28 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO DE N. 8457/2015</t>
+          <t>PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2015NE08487</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr"/>
+          <t>2015NE08449</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2/2015</t>
+        </is>
+      </c>
       <c r="C245" t="inlineStr">
         <is>
           <t>03/12/2015</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>2370506.22</v>
+        <v>1000000</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7725,19 +7733,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 8455/2015</t>
+          <t>PROC. DE DADOS</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2015NE08455</t>
+          <t>2015NE08472</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>235/2010</t>
+          <t>P.219/2014</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7746,7 +7754,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>2370506.22</v>
+        <v>167074.3</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7755,19 +7763,19 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>PROCESSAMENTO DE DADOS</t>
+          <t>INDENIZAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2015NE08471</t>
+          <t>2015NE08448</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>P.219/2014</t>
+          <t>235/2010</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7776,7 +7784,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>582322.04</v>
+        <v>990168.17</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7785,19 +7793,19 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SERV. PROCESSAMENTO DE DADOS</t>
+          <t>PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2015NE08448</t>
+          <t>2015NE08471</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>235/2010</t>
+          <t>P.219/2014</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7806,7 +7814,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>990168.17</v>
+        <v>582322.04</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7815,19 +7823,19 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>PROCESSAMENTO DE DADOS</t>
+          <t>SERV. PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2015NE08472</t>
+          <t>2015NE08455</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>P.219/2014</t>
+          <t>235/2010</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7836,7 +7844,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>167074.3</v>
+        <v>2370506.22</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7845,28 +7853,24 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>INDENIZAÇÃO</t>
+          <t>PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2015NE08449</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2/2015</t>
-        </is>
-      </c>
+          <t>2015NE08487</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
           <t>03/12/2015</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1000000</v>
+        <v>2370506.22</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7875,21 +7879,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>PROC. DE DADOS</t>
+          <t>ANULAÇÃO TOTAL DA NE 8455/2015</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2015NE08457</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>235/2010</t>
-        </is>
-      </c>
+          <t>2015NE08488</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
           <t>03/12/2015</t>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>PROCESSAMENTO DE DADOS</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO DE N. 8457/2015</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2023NE0003892</t>
+          <t>2023NE0003893</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7956,7 +7956,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1759989.84</v>
+        <v>2868935.74</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7965,19 +7965,19 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS PARA A MANUNTENÇÃO OPERACIONAL DO SIGEAM DA SEDUC/AM TC: 014/2018 AD: 04.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 023/2021 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2023NE0003893</t>
+          <t>2023NE0003892</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>2868935.74</v>
+        <v>1759989.84</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 023/2021 AD: 01.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS PARA A MANUNTENÇÃO OPERACIONAL DO SIGEAM DA SEDUC/AM TC: 014/2018 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -8032,7 +8032,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2023NE03350</t>
+          <t>2023NE0003350</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8055,14 +8055,14 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>6º Termo Aditivo ao Contrato 054/2027</t>
+          <t>ATENDER DESPESAS DO 6º TA AO CT-0054/2017-SEDUC, REF. A SERVIÇOS DE CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM PARA USO E MANUTENÇÃO DO SISTEMA DE GESTÃO E PROJETOS - SIGPRO PROC. ADM. 01.01.028101.010886</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2023NE0003350</t>
+          <t>2023NE03350</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>ATENDER DESPESAS DO 6º TA AO CT-0054/2017-SEDUC, REF. A SERVIÇOS DE CUSTOMIZAÇÃO, IMPLANTAÇÃO E HOSPEDAGEM PARA USO E MANUTENÇÃO DO SISTEMA DE GESTÃO E PROJETOS - SIGPRO PROC. ADM. 01.01.028101.010886</t>
+          <t>6º Termo Aditivo ao Contrato 054/2027</t>
         </is>
       </c>
     </row>
@@ -8152,12 +8152,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2022NE0000246</t>
+          <t>2022NE0000243</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>5835123.53</v>
+        <v>296020.56</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SERVICOS TÉCNICOS PROFISSIONAIS DE TIC;SERVIÇO DE OPERAÇÃO E GESTÃO DE CENTRAL DE ATENDIMENTO MULTICANAIS. SALDO REMANESCENTE;COMPLEMENTO DE QB;2021NE1504;CT 23/2021;;R$ 17.505.370,65</t>
+          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO DE EXECUÇÃO DO SISTEMA PRODAMRH - FOLHA DE PESSOAL E CADASTRO DE SERVIDOR. SALDO REMANESCENTE;COMPLEMENTO DE QB;2021NE372;CT 2/2021;;R$ 3.552.246,72</t>
         </is>
       </c>
     </row>
@@ -8212,12 +8212,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2022NE0000243</t>
+          <t>2022NE0000246</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>296020.56</v>
+        <v>5835123.53</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO E MANUTENÇÃO DE SOFTWARE;SERVIÇO DE EXECUÇÃO DO SISTEMA PRODAMRH - FOLHA DE PESSOAL E CADASTRO DE SERVIDOR. SALDO REMANESCENTE;COMPLEMENTO DE QB;2021NE372;CT 2/2021;;R$ 3.552.246,72</t>
+          <t>SERVICOS TÉCNICOS PROFISSIONAIS DE TIC;SERVIÇO DE OPERAÇÃO E GESTÃO DE CENTRAL DE ATENDIMENTO MULTICANAIS. SALDO REMANESCENTE;COMPLEMENTO DE QB;2021NE1504;CT 23/2021;;R$ 17.505.370,65</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025NE0000648</t>
+          <t>2025NE0000367</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1458780.89</v>
+        <v>312407.04</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 04.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8444,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025NE0000367</t>
+          <t>2025NE0000648</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>312407.04</v>
+        <v>1458780.89</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8467,19 +8467,19 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 04.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2024NE0000011</t>
+          <t>2024NE0000469</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>296020.56</v>
+        <v>2916974.27</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 02.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -8534,12 +8534,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2024NE0000469</t>
+          <t>2024NE0000011</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>2916974.27</v>
+        <v>296020.56</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8557,19 +8557,19 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM CONTACT CENTER COM ADOÇÃO DE PLATAFORMA DE INTEGRAÇÃO DE MULTICANAIS E MODULO DES GESTÃO DE ATENDIMENTO DA SEDUC/AM TC: 0023/2021 AD: 03.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA-FOLHA DE PAGAMENTO DE PESSOAL E CADASTRO DE SERVIDORES DA SEDUC/AM TC: 0002/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2023NE0000013</t>
+          <t>2023NE0000011</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>14/2018</t>
+          <t>23/2021</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>9428517</v>
+        <v>4376342.66</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM REF AO 4º TERMO ADITIVO AO CONTRATO Nº 14/2018, FIRMADO COM ESTA SECRETARIA PELO PERÍODO </t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE CONTACT CENTER, COM ADOÇÃO DE INTEGRAÇÃO DE MULTICANAIS E MÓDULO DE GESTÃO DE ATENDIMENTO REF AO 1º TERMO ADITIVO AO CONTRATO Nº 23/2021, A SER FIRMADO COM ESTA SECRETARIA P</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2023NE0000011</t>
+          <t>2023NE0000013</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>23/2021</t>
+          <t>14/2018</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>4376342.66</v>
+        <v>9428517</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8647,24 +8647,28 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE CONTACT CENTER, COM ADOÇÃO DE INTEGRAÇÃO DE MULTICANAIS E MÓDULO DE GESTÃO DE ATENDIMENTO REF AO 1º TERMO ADITIVO AO CONTRATO Nº 23/2021, A SER FIRMADO COM ESTA SECRETARIA P</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A MANUTENÇÃO OPERACIONAL, CORRETIVA E EVOLUTIVA DO SIGEAM REF AO 4º TERMO ADITIVO AO CONTRATO Nº 14/2018, FIRMADO COM ESTA SECRETARIA PELO PERÍODO </t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2019NE00003</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr"/>
+          <t>2019NE00019</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2/2015</t>
+        </is>
+      </c>
       <c r="C277" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>488852.12</v>
+        <v>244426.02</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8673,7 +8677,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO Nº 001/2019</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL DA SEDUC.</t>
         </is>
       </c>
     </row>
@@ -8710,21 +8714,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2019NE00019</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2/2015</t>
-        </is>
-      </c>
+          <t>2019NE00003</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>244426.02</v>
+        <v>488852.12</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8733,19 +8733,19 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL DA SEDUC.</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO Nº 001/2019</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2017NE00116</t>
+          <t>2017NE00211</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>161/2016</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>244425.99</v>
+        <v>7443106.4</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>PARA ATENDER NOS SERVIÇOS DE PROCESSAMENTO DE DADOS DAS FOLHAS DE PAGAMENTO DE PESSOAL E CADASTRO DOS SERVIDORES DESTA SECRETARIA</t>
+          <t>PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
@@ -8800,12 +8800,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2017NE00211</t>
+          <t>2017NE00116</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>161/2016</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>7443106.4</v>
+        <v>244425.99</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8823,19 +8823,19 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>PROCESSAMENTO DE DADOS</t>
+          <t>PARA ATENDER NOS SERVIÇOS DE PROCESSAMENTO DE DADOS DAS FOLHAS DE PAGAMENTO DE PESSOAL E CADASTRO DOS SERVIDORES DESTA SECRETARIA</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2014NE00478</t>
+          <t>2014NE00458</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>156/2013</t>
+          <t>235/2010</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>2400000</v>
+        <v>12674159.97</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -8853,19 +8853,19 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Contrato No. 156/2013 - Serviços de Implantação da Rede de Comunicação sem fio WI FI</t>
+          <t>Contrato No. 235/2010 - SIGEAM</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2014NE00458</t>
+          <t>2014NE00478</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>235/2010</t>
+          <t>156/2013</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>12674159.97</v>
+        <v>2400000</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Contrato No. 235/2010 - SIGEAM</t>
+          <t>Contrato No. 156/2013 - Serviços de Implantação da Rede de Comunicação sem fio WI FI</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SEDUC/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEDUC/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-06-30</t>
         </is>
       </c>
     </row>
